--- a/题库模板.xlsx
+++ b/题库模板.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题库" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,8 +413,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -434,20 +445,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>难度</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>知识点</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>选项A</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>选项B</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>选项C</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>选项D</t>
         </is>
@@ -461,18 +482,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>养老护理的基本原则是“安全第一”。</t>
+          <t>汉语拼音的声母共有 23 个。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -482,18 +509,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>老年人每天应摄入不少于2000ml的水。</t>
+          <t>“日”字是象形字。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,345 +536,5051 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>测量血压前应让老年人静坐至少5分钟。</t>
+          <t>“蜻蜓”两个字的偏旁都是“虫”。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>判断题</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>老年人正常体温（腋下）范围是？</t>
+          <t>“的”“地”“得”三个字的用法完全相同。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>×</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36.0-37.0℃</t>
+          <t>中</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.3-37.2℃</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>37.0-38.0℃</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>35.5-36.5℃</t>
+          <t>第四章 古诗文积累</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>判断题</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>测量血压时袖带下缘应位于肘窝上方多高？</t>
+          <t>“春眠不觉晓”的作者是李白。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>×</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1-2cm</t>
+          <t>难</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2-3cm</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2.5-4cm</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>4-5cm</t>
+          <t>第五章 文学常识</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>判断题</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老年人每日适宜的食盐摄入量不超过？</t>
+          <t>“弯弯的月亮像小船”是比喻句。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>√</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3g</t>
+          <t>易</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6g</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>10g</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>12g</t>
+          <t>第一章 拼音与汉字</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>判断题</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>协助老年人翻身时，应注意避免的动作是？</t>
+          <t>“人多力量大”是一句谚语。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>√</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>托住头部</t>
+          <t>易</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>托住腰部</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>托住臀部</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>用力拖拽</t>
+          <t>第二章 词语与成语</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>单选题</t>
+          <t>判断题</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>老年人最适宜的室内温度为？</t>
+          <t>拼音“ü”和“j、q、x”相拼时要省略两点。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>√</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16-18℃</t>
+          <t>中</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18-20℃</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>22-26℃</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>28-30℃</t>
+          <t>第三章 句子与标点</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>多选题</t>
+          <t>判断题</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>以下哪些属于养老护理员的职业道德规范？</t>
+          <t>“认真”的近义词是“马虎”。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ABD</t>
+          <t>×</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>尊老敬老</t>
+          <t>中</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>爱岗敬业</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>追求利润</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>保护隐私</t>
+          <t>第四章 古诗文积累</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>多选题</t>
+          <t>判断题</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>老年人常见的意外伤害包括？</t>
+          <t>“三心二意”形容做事非常专心。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>×</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>跌倒</t>
+          <t>难</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>烫伤</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>噎食</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>感冒</t>
+          <t>第五章 文学常识</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>多选题</t>
+          <t>判断题</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>测量体温的常用部位包括？</t>
+          <t>“千里之行，始于足下”出自《老子》。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ACD</t>
+          <t>√</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>腋下</t>
+          <t>易</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>口腔</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>直肠</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>标点符号“？”表示疑问的语气。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>“碧玉妆成一树高”描写的是柳树。</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>“他跑得很快”中的“得”用得正确。</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>“森”是会意字。</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>“小朋友”是名词。</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>“不但……而且……”表示转折关系。</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>《西游记》的作者是吴承恩。</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>“漂亮”和“美丽”是一对反义词。</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>“一”字只有一笔。</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>“他今天没来，因为他生病了”中的“因为”表示原因。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>拼音中“l”和“n”的发音完全相同。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>“坐井观天”比喻见识广博。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>“欲穷千里目，更上一层楼”出自《登鹳雀楼》。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>“啊、呀、吗、呢”都是语气词。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>“绿油油”是 ABB 式的词语。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>“一鼓作气”中的“鼓”意思是敲鼓。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>所有汉字的笔画数都相同。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>“我的书包”中“我的”是定语。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>“春风又绿江南岸”的作者是王安石。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>“灿烂”的“灿”读作 càn。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>“守株待兔”比喻勤奋努力。</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>顿号“、”用于句子内部的并列词语之间。</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>“骄傲”这个词只有贬义。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>“亡羊补牢”中的“亡”意思是丢失。</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>拼音中“zh、ch、sh”是翘舌音。</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>“他十分高兴”中的“十分”是程度副词。</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>“峨眉山月半轮秋”的作者是杜甫。</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>排比是用三个或三个以上结构相似的句子。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>判断题</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>“明”由“日”和“月”组成，是会意字。</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>√</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>“蝴蝶”的正确读音是？</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>hú dié</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>hú tié</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>fú dié</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>hú diē</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>“儿童急走追黄蝶”的下一句是？</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>飞入菜花无处寻</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>忙趁东风放纸鸢</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>树头新绿未成阴</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>篱落疏疏一径深</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>《静夜思》的作者是？</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>杜甫</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>李白</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>白居易</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>王维</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>“春”字的部首是？</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>下列词语书写完全正确的是？</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>完璧归赵</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>完壁归赵</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>完碧归赵</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>完闭归赵</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>“忐忑不安”中“忐忑”的意思是？</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>心情平静</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>心神不定</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>非常高兴</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>十分生气</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>“一日不见，如隔三秋”中的“三秋”指？</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>三个秋天</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>很长的时间</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>整整三年</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>三个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>下列句子中是比喻句的是？</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>他长得很像他爸爸</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>弯弯的月亮像小船</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>我好像见过他</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>他好像不太高兴</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>“停车坐爱枫林晚”中“坐”的意思是？</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>坐下</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>乘坐</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>座位</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>“虽然……但是……”表示什么关系？</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>因果关系</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>转折关系</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>并列关系</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>递进关系</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>下列词语属于 AABB 式的是？</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>高高兴兴</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>绿油油</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>研究研究</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>一心一意</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>“李白乘舟将欲行”出自哪首诗？</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>《赠汪伦》</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>《望庐山瀑布》</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>《早发白帝城》</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>《黄鹤楼送孟浩然之广陵》</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>“典”字共有几画？</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6 画</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>7 画</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8 画</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>9 画</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>“（　）的阳光洒满大地”，横线上应填？</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>温暖</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>温柔</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>温和</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>温热</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>下列句子标点使用正确的是？</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>他说：“我明天去。”</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>他说：“我明天去”。</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>他说“我明天去。”</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>他说，我明天去。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>“千里冰封，万里雪飘”描写的是哪个季节？</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>春天</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>夏天</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>秋天</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>冬天</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>“聪明”的反义词是？</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>机灵</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>愚蠢</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>智慧</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>伶俐</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>“一叶知秋”的意思是？</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>看见一片落叶就知道秋天到了</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>秋天只有一片叶子</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>叶子很有用处</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>秋天非常寒冷</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>“苹果、香蕉、橘子”这三个词都属于？</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>主食</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>零食</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>把“他把作业写完了”改成“被”字句，正确的是？</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>作业被他写完了</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>他被作业写完了</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>作业把他写完了</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>他被写完了作业</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>“桂林山水甲天下”中的“甲”意思是？</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>第一</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>铠甲</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>指甲</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>甲乙</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>下列词语搭配不当的是？</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>明亮的眼睛</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>清脆的声音</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>香甜的歌声</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>温暖的阳光</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>“野火烧不尽，春风吹又生”描写的是？</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>竹子</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>小草</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>梅花</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>松树</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>“他一边唱歌一边跳舞”中“一边……一边……”表示？</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>并列关系</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>转折关系</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>因果关系</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>选择关系</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>“忐忑”两个字的偏旁都是？</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>心</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>卜</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>下列句子没有语病的是？</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>通过这次活动，使我懂得了道理</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>这次活动使我懂得了道理</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>通过这次活动，使我明白</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>使我懂得了道理</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>“黄河远上白云间”的下一句是？</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>一片孤城万仞山</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>春风不度玉门关</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>大漠孤烟直</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>长河落日圆</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>“圆”字的部首是？</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>口</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>圆</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>囗</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>“文思泉涌”形容的是？</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>文笔很差</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>思路敏捷</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>身体很好</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>声音洪亮</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>“他跑得飞快”中“得”的作用是？</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>表示可能</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>连接补语</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>表示完成</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>表示疑问</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>下列句子属于拟人句的是？</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>小鸟在枝头唱歌</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>小鸟像歌手一样</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>小鸟飞走了</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>小鸟非常可爱</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>“床前明月光”的作者是？</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>李白</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>杜甫</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>王维</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>孟浩然</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>“亡羊补牢”中的“牢”意思是？</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>牢固</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>羊圈</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>监牢</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>劳动</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>“（　）的溪水唱着歌向前流去”，横线上应填？</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>清澈</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>清楚</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>清爽</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>清晰</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>下列句子中“一”读作 yí 的是？</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>一起</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>一个</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>一天</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>一半</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>“（　）地说：‘我做到了！’”，横线上应填？</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>兴奋</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>兴趣</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>高兴奋</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>高兴兴</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>“山重水复疑无路”的下一句是？</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>柳暗花明又一村</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>一枝红杏出墙来</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>万紫千红总是春</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>春色满园关不住</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>“近朱者赤，近墨者黑”说明了？</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>环境对人的影响很大</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>颜色非常重要</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>要远离所有朋友</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>墨汁是黑色的</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>“（　）的天空飘着几朵白云”，横线上应填？</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>蔚蓝</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>蔚然</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>蓝蔚</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>蓝蓝的的</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>“燕子去了，有再来的时候；杨柳枯了，有再青的时候；桃花谢了，有再开的时候。”主要运用了什么修辞手法？</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>拟人</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>比喻</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>夸张</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>排比</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>“遥知不是雪，为有暗香来”描写的是？</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>梅花</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>雪花</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>桃花</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>菊花</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>“字正腔圆”形容的是？</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>说话吐字清楚、声音圆润</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>字写得很好看</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>唱歌非常好听</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>文章写得很好</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>“他高兴得跳了起来”中补语是？</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>他</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>高兴</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>跳了起来</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>得</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>下列成语形容学习勤奋的是？</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>悬梁刺股</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>守株待兔</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>画蛇添足</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>叶公好龙</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>“一”在“一群”中读作？</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>yī</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>yí</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>yì</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>yǐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>“书山有路勤为径”的下一句是？</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>学海无涯苦作舟</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>一寸光阴一寸金</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>少壮不努力</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>老大徒伤悲</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>“赞叹不已”中的“已”意思是？</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>已经</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>自己</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>以后</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>下列词语中与“秀丽”意思最接近的是？</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>清秀</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>丑陋</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>强壮</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>高大</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>下列句子标点使用不正确的是？</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>今天天气真好！</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>你去哪儿？</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>我喜欢读书。</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>他问我：你好吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>单选题</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>“锄禾日当午，汗滴禾下土”的作者是？</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>李绅</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>李白</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>杜甫</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>白居易</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>多选题</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>以下哪些因素会影响老年人的睡眠质量？</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>下列属于中国四大名著的有？</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>《红楼梦》</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>《西游记》</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>《水浒传》</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>《聊斋志异》</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>下列词语互为近义词的有？</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ABD</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>美丽—漂亮</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>高兴—快乐</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>认真—马虎</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>立刻—马上</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>下列诗句描写春天景色的有？</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ABD</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>春眠不觉晓</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>处处闻啼鸟</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>停车坐爱枫林晚</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>春色满园关不住</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>下列汉字属于象形字的有？</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>山</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>明</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>下列标点符号使用正确的有？</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>他问：“你去吗？”</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>花园里有花、草、树。</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>你好吗？</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>他说“我来了。”</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>下列词语属于 ABB 式的有？</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>绿油油</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>红彤彤</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>亮晶晶</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>高高兴兴</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>下列属于李白作品的有？</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>《静夜思》</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>《望庐山瀑布》</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>《赠汪伦》</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>《春望》</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>下列句子使用了比喻修辞的有？</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ABD</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>弯弯的月亮像小船</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>他跑得像一阵风</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>小鸟在枝头唱歌</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>太阳像一个大火球</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>下列词语中没有错别字的有？</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>一心一意</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>全神贯注</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>废寝忘食</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>专心至志</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>下列属于描写人物品质的词语有？</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>诚实</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>勇敢</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>善良</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>高大</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>下列“的、地、得”使用正确的有？</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>美丽的风景</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>慢慢地走</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>跑得很快</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>高兴的跳起来</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>下列属于语气词的有？</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>吗</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>呢</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>吧</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>下列各组词语互为近义词的有？</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>快乐—愉快</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>安静—宁静</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>骄傲—自豪</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>高大—矮小</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>下列属于成语的有？</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>亡羊补牢</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>画蛇添足</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>一叶知秋</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>吃早饭</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>下列属于“唐宋八大家”的有？</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>韩愈</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>柳宗元</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>苏轼</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>李白</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>下列“把”字句使用正确的有？</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>我把作业写完了</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>他把门关上了</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>我把书放在桌上</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>我把书被拿走了</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>下列词语可以用来描写夏天的有？</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ABD</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>烈日炎炎</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>骄阳似火</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>白雪皑皑</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>挥汗如雨</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>下列句子属于拟人句的有？</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>花儿在向我微笑</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>小草偷偷地钻出地面</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>小鸟在树上唱歌</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>他像小鸟一样快</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>下列汉字属于左右结构的有？</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>明</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>林</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>田</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>下列属于中国古代四大发明的有？</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>环境噪音</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>身体不适</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>心理因素</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>咖啡因摄入</t>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>造纸术</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>印刷术</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>指南针</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>火药</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>下列词语可以用来形容声音的有？</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>清脆</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>洪亮</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>悦耳</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>柔软</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>下列句子属于反问句的有？</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>难道这不是你的吗？</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>你怎么能这样做呢？</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>这不是很好吗？</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>你是谁？</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>下列属于《西游记》中人物的有？</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>孙悟空</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>猪八戒</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>唐僧</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>林黛玉</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>下列词语中“一”读作 yì 的有？</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>一天</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>一起</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>一群</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>一个</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>下列可以用来描写秋天的有？</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ABD</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>停车坐爱枫林晚</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>秋高气爽</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>春眠不觉晓</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>大雁南飞</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>下列句子没有语病的有？</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ACD</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>我们要爱护环境</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>他大约十岁左右</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>同学们都很高兴</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>我们要养成讲卫生的好习惯</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>下列属于关联词语的有？</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>因为……所以……</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>虽然……但是……</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>不但……而且……</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>早上……晚上……</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>下列汉字属于独体字的有？</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>明</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>下列各组词语互为近义词的有？</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ABD</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>立刻—马上</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>忽然—突然</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>快乐—悲伤</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>仔细—认真</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>多选题</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>下列属于儿童文学作品中人物的有？</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>孙悟空</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>白雪公主</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>卖火柴的小女孩</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>曹操</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>请写出《静夜思》全诗，并说说它表达了诗人怎样的思想感情。</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>床前明月光，疑是地上霜。举头望明月，低头思故乡。全诗通过描写客居他乡时所见到的月光，表达了诗人对故乡的深切思念之情。</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>请写出“守株待兔”的意思，并说明它告诉我们什么道理。</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>守株待兔：守着树桩等待兔子撞上来。比喻死守狭隘经验、不知变通，或妄想不劳而获。道理：不能把偶然的侥幸当成常态，只有踏实劳动才有收获。</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>请把“他把作业写完了”改写成“被”字句，并说说改写后句子的表达重点有什么变化。</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>改写：作业被他写完了。原句强调的是“他”做了什么，改写后强调的是“作业”怎么样了——陈述的对象由施动者变成了受动者。</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>“弯弯的月亮像一只小船。”这句话运用了什么修辞手法？请说明理由。</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>运用了比喻。理由：句中有本体“月亮”、喻体“小船”和比喻词“像”，并且月亮和小船在“弯弯的”这个形状特征上相似，是把月亮比作小船。</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>请写出三个描写春天景色的四字词语，并任选其中一个造一个句子。</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>示例：春暖花开、鸟语花香、万紫千红。造句：春天到了，公园里春暖花开，游人络绎不绝。</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>请给下面这句话加上合适的标点符号：今天天气真好我们一起去公园放风筝吧</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>今天天气真好，我们一起去公园放风筝吧！句中的停顿用逗号，句末表示祈使和感叹的语气用感叹号。</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>第一章 拼音与汉字</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>请写出两句描写友情的古诗，并注明作者。</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>示例一：桃花潭水深千尺，不及汪伦送我情。——李白《赠汪伦》。示例二：海内存知己，天涯若比邻。——王勃《送杜少府之任蜀州》。</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>第二章 词语与成语</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>请说出“的”“地”“得”三个字的用法区别，并各造一个句子。</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>“的”用在定语和名词之间，如“美丽的花朵”；“地”用在状语和动词之间，如“他飞快地跑”；“得”用在动词或形容词和补语之间，如“他跑得飞快”。</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>第三章 句子与标点</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>请用“不但……而且……”造一个句子，并说明这组关联词语表示什么关系。</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>示例：他不但学习好，而且乐于助人。“不但……而且……”表示递进关系，后一个分句比前一个分句意思更进一层。</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>第四章 古诗文积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>简答题</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>请用一段话（不少于 50 字）介绍你最喜欢的一本课外书，说清楚书名、主要内容和推荐理由。</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>答案开放，言之成理即可。要求包含三点：① 书名；② 主要内容概括；③ 推荐理由（如情节吸引人、人物形象鲜明、给自己带来启发等），语句通顺。</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>第五章 文学常识</t>
         </is>
       </c>
     </row>
